--- a/cylineder_measurements.xlsx
+++ b/cylineder_measurements.xlsx
@@ -38,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,6 +49,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -85,10 +91,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -403,8 +409,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="24.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="26.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -451,7 +457,7 @@
         <v>22.2101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -462,7 +468,7 @@
         <v>22.21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -473,7 +479,7 @@
         <v>22.205</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -484,7 +490,7 @@
         <v>22.208</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -495,7 +501,7 @@
         <v>22.209</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -506,7 +512,7 @@
         <v>22.21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -517,7 +523,7 @@
         <v>22.215</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -528,7 +534,7 @@
         <v>22.221</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -539,7 +545,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -550,7 +556,7 @@
         <v>22.204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -561,7 +567,7 @@
         <v>22.21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -572,7 +578,7 @@
         <v>22.213</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -583,7 +589,7 @@
         <v>22.204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -594,7 +600,7 @@
         <v>22.205</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -605,7 +611,7 @@
         <v>22.204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -616,7 +622,7 @@
         <v>22.223</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -627,7 +633,7 @@
         <v>22.214</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
